--- a/AAII_Financials/Yearly/BN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BN_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Yearly/BN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
   <si>
     <t>BN</t>
   </si>
@@ -656,147 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>95924000</v>
+      </c>
+      <c r="E8" s="3">
         <v>92769000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>75731000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>62752000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>67826000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>56771000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>40786000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>24411000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>19913000</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>52224000</v>
+      </c>
+      <c r="E9" s="3">
         <v>54044000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>44149000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>35150000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>41463000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>37506000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>26461000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12487000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>9988000</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>43700000</v>
+      </c>
+      <c r="E10" s="3">
         <v>38725000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>31582000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>27602000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>26363000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>19265000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>14325000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>11924000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9925000</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -809,8 +821,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -838,9 +851,12 @@
       <c r="K12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -868,9 +884,12 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -898,39 +917,45 @@
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>9075000</v>
+      </c>
+      <c r="E15" s="3">
         <v>7683000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>6437000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5791000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4876000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>3102000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2345000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2020000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1695000</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -940,68 +965,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>89808000</v>
+      </c>
+      <c r="E17" s="3">
         <v>86105000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>61019000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>61208000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>61977000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>49531000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>35622000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>21418000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>15048000</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>6116000</v>
+      </c>
+      <c r="E18" s="3">
         <v>6664000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>14712000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1544000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5849000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7240000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5164000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2993000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>4865000</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1014,8 +1046,9 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1043,39 +1076,45 @@
       <c r="K20" s="3">
         <v>0</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>15191000</v>
+      </c>
+      <c r="E21" s="3">
         <v>14347000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>21149000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7335000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>10725000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>10342000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>7509000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5013000</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1103,69 +1142,78 @@
       <c r="K22" s="3">
         <v>0</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>6116000</v>
+      </c>
+      <c r="E23" s="3">
         <v>6664000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>14712000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1544000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5849000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7240000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5164000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2993000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4865000</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1011000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1469000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2324000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>837000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>495000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-248000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>613000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-345000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>196000</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1193,69 +1241,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5105000</v>
+      </c>
+      <c r="E26" s="3">
         <v>5195000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>12388000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>707000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5354000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7488000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>4551000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3338000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4669000</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>964000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1906000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3818000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-275000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>2655000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3433000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1317000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1518000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2207000</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1283,9 +1340,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1313,9 +1373,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1343,9 +1406,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1373,9 +1439,12 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1403,39 +1472,45 @@
       <c r="K32" s="3">
         <v>0</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>964000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1906000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3818000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-275000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>2655000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3433000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1317000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1518000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2207000</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1463,74 +1538,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>964000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1906000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3818000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-275000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>2655000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3433000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1317000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1518000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2207000</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1543,8 +1627,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1557,38 +1642,42 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11222000</v>
+      </c>
+      <c r="E41" s="3">
         <v>14396000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>12694000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>9933000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6778000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8390000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5139000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>4299000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2774000</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1616,99 +1705,111 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14879000</v>
+      </c>
+      <c r="E43" s="3">
         <v>14155000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11332000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10113000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>11129000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>9167000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7209000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4294000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7044000</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>11412000</v>
+      </c>
+      <c r="E44" s="3">
         <v>12843000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>11415000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>10360000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>10272000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6989000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6311000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5349000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5281000</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>11363000</v>
+      </c>
+      <c r="E45" s="3">
         <v>10557000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8162000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6335000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5636000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5508000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3350000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3448000</v>
       </c>
-      <c r="K45" s="3" t="s">
+      <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -1736,99 +1837,111 @@
       <c r="K46" s="3">
         <v>0</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L46" s="3">
+        <v>0</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>87448000</v>
+      </c>
+      <c r="E47" s="3">
         <v>73993000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>62646000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>59057000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>53166000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>39874000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>36794000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>29677000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>29372000</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>271769000</v>
+      </c>
+      <c r="E48" s="3">
         <v>239368000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>216354000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>196791000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>185950000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>151603000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>109875000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>99518000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>84437000</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>73905000</v>
+      </c>
+      <c r="E49" s="3">
         <v>67073000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>50836000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>39372000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>42260000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>27577000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>19559000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>9856000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>7713000</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1856,9 +1969,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1886,39 +2002,45 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>8097000</v>
+      </c>
+      <c r="E52" s="3">
         <v>8899000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>17564000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11650000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>8669000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6840000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4093000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>2998000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2893000</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1946,39 +2068,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>490095000</v>
+      </c>
+      <c r="E54" s="3">
         <v>441284000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>391003000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>343696000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>323969000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>256281000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>192720000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>159826000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>139514000</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1991,8 +2119,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2005,68 +2134,75 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>50011000</v>
+      </c>
+      <c r="E57" s="3">
         <v>48559000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>43505000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>42459000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>29084000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>23740000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>17821000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11879000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11276000</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>58175000</v>
+      </c>
+      <c r="E58" s="3">
         <v>43297000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>31879000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>21287000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>16329000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11624000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10778000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8973000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>11484000</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -2094,9 +2230,12 @@
       <c r="K59" s="3">
         <v>0</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2124,69 +2263,78 @@
       <c r="K60" s="3">
         <v>0</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L60" s="3">
+        <v>0</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>188299000</v>
+      </c>
+      <c r="E61" s="3">
         <v>182357000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>155864000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>137580000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>143275000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>108995000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>69857000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>58080000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>48946000</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>24987000</v>
+      </c>
+      <c r="E62" s="3">
         <v>23190000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>20328000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>15913000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>14849000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>12236000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11409000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>9640000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8785000</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2214,9 +2362,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2244,9 +2395,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2274,39 +2428,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>444318000</v>
+      </c>
+      <c r="E66" s="3">
         <v>397531000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>344648000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>307858000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>288956000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>226466000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>164476000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>133373000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>114207000</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2319,8 +2479,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2348,9 +2509,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2378,14 +2542,17 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>4145000</v>
+        <v>4103000</v>
       </c>
       <c r="E70" s="3">
         <v>4145000</v>
@@ -2397,20 +2564,23 @@
         <v>4145000</v>
       </c>
       <c r="H70" s="3">
+        <v>4145000</v>
+      </c>
+      <c r="I70" s="3">
         <v>4168000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>4192000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>3954000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>3739000</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2438,39 +2608,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19692000</v>
+      </c>
+      <c r="E72" s="3">
         <v>18904000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>19115000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15952000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>16408000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>14551000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11899000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11182000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>10507000</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2498,9 +2674,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2528,9 +2707,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2558,39 +2740,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>41674000</v>
+      </c>
+      <c r="E76" s="3">
         <v>39608000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>42210000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>31693000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>30868000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>25647000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>24052000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>22499000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>21568000</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2618,74 +2806,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>964000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1906000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3818000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-275000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>2655000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3433000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1317000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1518000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2207000</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2698,38 +2895,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9075000</v>
+      </c>
+      <c r="E83" s="3">
         <v>7683000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6437000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5791000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4876000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3102000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2345000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2020000</v>
       </c>
-      <c r="K83" s="3" t="s">
+      <c r="L83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2757,9 +2958,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2787,9 +2991,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2817,9 +3024,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2847,9 +3057,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2877,39 +3090,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>6456000</v>
+      </c>
+      <c r="E89" s="3">
         <v>8909000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7667000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8364000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6321000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5158000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3985000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3083000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2574000</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2922,38 +3141,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-16282000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-16900000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18167000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9123000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9974000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4841000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3804000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3441000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3095000</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2981,9 +3204,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3011,39 +3237,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-29762000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-39650000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-21045000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13873000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-36674000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-19833000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11394000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8557000</v>
       </c>
-      <c r="K94" s="3" t="s">
+      <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3056,38 +3288,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-602000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-1029000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-1486000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-867000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-772000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-726000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-685000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-633000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-542000</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3115,9 +3351,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3145,9 +3384,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3175,97 +3417,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>19927000</v>
+      </c>
+      <c r="E100" s="3">
         <v>32460000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>16261000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>8698000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>28746000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>18136000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>8185000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6993000</v>
       </c>
-      <c r="K100" s="3" t="s">
+      <c r="L100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>205000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-17000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-122000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-34000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-210000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>64000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>6000</v>
       </c>
-      <c r="K101" s="3" t="s">
+      <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3174000</v>
+      </c>
+      <c r="E102" s="3">
         <v>1702000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2761000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3155000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1612000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3251000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>840000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1525000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-503000</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>BN</t>
   </si>
@@ -714,25 +714,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>95924000</v>
+        <v>97992000</v>
       </c>
       <c r="E8" s="3">
-        <v>92769000</v>
+        <v>95382000</v>
       </c>
       <c r="F8" s="3">
-        <v>75731000</v>
+        <v>78182000</v>
       </c>
       <c r="G8" s="3">
-        <v>62752000</v>
+        <v>62673000</v>
       </c>
       <c r="H8" s="3">
-        <v>67826000</v>
+        <v>71609000</v>
       </c>
       <c r="I8" s="3">
-        <v>56771000</v>
+        <v>58489000</v>
       </c>
       <c r="J8" s="3">
-        <v>40786000</v>
+        <v>41999000</v>
       </c>
       <c r="K8" s="3">
         <v>24411000</v>
@@ -747,25 +747,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>52224000</v>
+        <v>77808000</v>
       </c>
       <c r="E9" s="3">
-        <v>54044000</v>
+        <v>75507000</v>
       </c>
       <c r="F9" s="3">
-        <v>44149000</v>
+        <v>64000000</v>
       </c>
       <c r="G9" s="3">
-        <v>35150000</v>
+        <v>53177000</v>
       </c>
       <c r="H9" s="3">
-        <v>41463000</v>
+        <v>52728000</v>
       </c>
       <c r="I9" s="3">
-        <v>37506000</v>
+        <v>45519000</v>
       </c>
       <c r="J9" s="3">
-        <v>26461000</v>
+        <v>32388000</v>
       </c>
       <c r="K9" s="3">
         <v>12487000</v>
@@ -780,25 +780,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>43700000</v>
+        <v>20184000</v>
       </c>
       <c r="E10" s="3">
-        <v>38725000</v>
+        <v>19875000</v>
       </c>
       <c r="F10" s="3">
-        <v>31582000</v>
+        <v>14182000</v>
       </c>
       <c r="G10" s="3">
-        <v>27602000</v>
+        <v>9496000</v>
       </c>
       <c r="H10" s="3">
-        <v>26363000</v>
+        <v>18881000</v>
       </c>
       <c r="I10" s="3">
-        <v>19265000</v>
+        <v>12970000</v>
       </c>
       <c r="J10" s="3">
-        <v>14325000</v>
+        <v>9611000</v>
       </c>
       <c r="K10" s="3">
         <v>11924000</v>
@@ -894,25 +894,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-4512000</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>-1397000</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-8232000</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>272000</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>-1837000</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-784000</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -972,25 +972,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>89808000</v>
+        <v>81478000</v>
       </c>
       <c r="E17" s="3">
-        <v>86105000</v>
+        <v>78633000</v>
       </c>
       <c r="F17" s="3">
-        <v>61019000</v>
+        <v>64116000</v>
       </c>
       <c r="G17" s="3">
-        <v>61208000</v>
+        <v>53278000</v>
       </c>
       <c r="H17" s="3">
-        <v>61977000</v>
+        <v>57702000</v>
       </c>
       <c r="I17" s="3">
-        <v>49531000</v>
+        <v>48725000</v>
       </c>
       <c r="J17" s="3">
-        <v>35622000</v>
+        <v>34828000</v>
       </c>
       <c r="K17" s="3">
         <v>21418000</v>
@@ -1005,25 +1005,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>6116000</v>
+        <v>16514000</v>
       </c>
       <c r="E18" s="3">
-        <v>6664000</v>
+        <v>16749000</v>
       </c>
       <c r="F18" s="3">
-        <v>14712000</v>
+        <v>14066000</v>
       </c>
       <c r="G18" s="3">
-        <v>1544000</v>
+        <v>9395000</v>
       </c>
       <c r="H18" s="3">
-        <v>5849000</v>
+        <v>13907000</v>
       </c>
       <c r="I18" s="3">
-        <v>7240000</v>
+        <v>9764000</v>
       </c>
       <c r="J18" s="3">
-        <v>5164000</v>
+        <v>7171000</v>
       </c>
       <c r="K18" s="3">
         <v>2993000</v>
@@ -1053,25 +1053,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-593000</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>780000</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>-18000</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>366000</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>821000</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>-493000</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>-817000</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1086,25 +1086,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>15191000</v>
+        <v>26182000</v>
       </c>
       <c r="E21" s="3">
-        <v>14347000</v>
+        <v>23652000</v>
       </c>
       <c r="F21" s="3">
-        <v>21149000</v>
+        <v>20521000</v>
       </c>
       <c r="G21" s="3">
-        <v>7335000</v>
+        <v>14820000</v>
       </c>
       <c r="H21" s="3">
-        <v>10725000</v>
+        <v>17962000</v>
       </c>
       <c r="I21" s="3">
-        <v>10342000</v>
+        <v>13359000</v>
       </c>
       <c r="J21" s="3">
-        <v>7509000</v>
+        <v>10333000</v>
       </c>
       <c r="K21" s="3">
         <v>5013000</v>
@@ -1119,25 +1119,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>15503000</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>10702000</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>7604000</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>7213000</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>7227000</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>4854000</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>3608000</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1290,16 +1290,16 @@
         <v>1906000</v>
       </c>
       <c r="F27" s="3">
-        <v>3818000</v>
+        <v>3792000</v>
       </c>
       <c r="G27" s="3">
-        <v>-275000</v>
+        <v>-182000</v>
       </c>
       <c r="H27" s="3">
-        <v>2655000</v>
+        <v>2581000</v>
       </c>
       <c r="I27" s="3">
-        <v>3433000</v>
+        <v>3328000</v>
       </c>
       <c r="J27" s="3">
         <v>1317000</v>
@@ -1449,25 +1449,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>593000</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-780000</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-366000</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>-821000</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>493000</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>817000</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1482,25 +1482,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>964000</v>
+        <v>1130000</v>
       </c>
       <c r="E33" s="3">
-        <v>1906000</v>
+        <v>2056000</v>
       </c>
       <c r="F33" s="3">
-        <v>3818000</v>
+        <v>3966000</v>
       </c>
       <c r="G33" s="3">
-        <v>-275000</v>
+        <v>-134000</v>
       </c>
       <c r="H33" s="3">
-        <v>2655000</v>
+        <v>2807000</v>
       </c>
       <c r="I33" s="3">
-        <v>3433000</v>
+        <v>3584000</v>
       </c>
       <c r="J33" s="3">
-        <v>1317000</v>
+        <v>1462000</v>
       </c>
       <c r="K33" s="3">
         <v>1518000</v>
@@ -1548,25 +1548,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>964000</v>
+        <v>1130000</v>
       </c>
       <c r="E35" s="3">
-        <v>1906000</v>
+        <v>2056000</v>
       </c>
       <c r="F35" s="3">
-        <v>3818000</v>
+        <v>3966000</v>
       </c>
       <c r="G35" s="3">
-        <v>-275000</v>
+        <v>-134000</v>
       </c>
       <c r="H35" s="3">
-        <v>2655000</v>
+        <v>2807000</v>
       </c>
       <c r="I35" s="3">
-        <v>3433000</v>
+        <v>3584000</v>
       </c>
       <c r="J35" s="3">
-        <v>1317000</v>
+        <v>1462000</v>
       </c>
       <c r="K35" s="3">
         <v>1518000</v>
@@ -1715,25 +1715,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>14879000</v>
+        <v>24783000</v>
       </c>
       <c r="E43" s="3">
-        <v>14155000</v>
+        <v>22107000</v>
       </c>
       <c r="F43" s="3">
-        <v>11332000</v>
+        <v>14169000</v>
       </c>
       <c r="G43" s="3">
-        <v>10113000</v>
+        <v>12809000</v>
       </c>
       <c r="H43" s="3">
-        <v>11129000</v>
+        <v>12988000</v>
       </c>
       <c r="I43" s="3">
-        <v>9167000</v>
+        <v>10985000</v>
       </c>
       <c r="J43" s="3">
-        <v>7209000</v>
+        <v>8823000</v>
       </c>
       <c r="K43" s="3">
         <v>4294000</v>
@@ -1781,25 +1781,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>11363000</v>
+        <v>2489000</v>
       </c>
       <c r="E45" s="3">
-        <v>10557000</v>
+        <v>2830000</v>
       </c>
       <c r="F45" s="3">
-        <v>8162000</v>
+        <v>11958000</v>
       </c>
       <c r="G45" s="3">
-        <v>6335000</v>
+        <v>5917000</v>
       </c>
       <c r="H45" s="3">
-        <v>5636000</v>
+        <v>3502000</v>
       </c>
       <c r="I45" s="3">
-        <v>5508000</v>
+        <v>2185000</v>
       </c>
       <c r="J45" s="3">
-        <v>3350000</v>
+        <v>1605000</v>
       </c>
       <c r="K45" s="3">
         <v>3448000</v>
@@ -1814,25 +1814,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>63539000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>65399000</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>60664000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>47749000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>40771000</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>35980000</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>26252000</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -1847,25 +1847,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>87448000</v>
+        <v>77544000</v>
       </c>
       <c r="E47" s="3">
-        <v>73993000</v>
+        <v>66041000</v>
       </c>
       <c r="F47" s="3">
-        <v>62646000</v>
+        <v>59809000</v>
       </c>
       <c r="G47" s="3">
-        <v>59057000</v>
+        <v>56361000</v>
       </c>
       <c r="H47" s="3">
-        <v>53166000</v>
+        <v>51307000</v>
       </c>
       <c r="I47" s="3">
-        <v>39874000</v>
+        <v>38056000</v>
       </c>
       <c r="J47" s="3">
-        <v>36794000</v>
+        <v>35180000</v>
       </c>
       <c r="K47" s="3">
         <v>29677000</v>
@@ -1889,16 +1889,16 @@
         <v>216354000</v>
       </c>
       <c r="G48" s="3">
-        <v>196791000</v>
+        <v>196876000</v>
       </c>
       <c r="H48" s="3">
-        <v>185950000</v>
+        <v>186059000</v>
       </c>
       <c r="I48" s="3">
-        <v>151603000</v>
+        <v>151936000</v>
       </c>
       <c r="J48" s="3">
-        <v>109875000</v>
+        <v>110265000</v>
       </c>
       <c r="K48" s="3">
         <v>99518000</v>
@@ -2011,26 +2011,26 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>8097000</v>
-      </c>
-      <c r="E52" s="3">
-        <v>8899000</v>
-      </c>
-      <c r="F52" s="3">
-        <v>17564000</v>
-      </c>
-      <c r="G52" s="3">
-        <v>11650000</v>
-      </c>
-      <c r="H52" s="3">
-        <v>8669000</v>
-      </c>
-      <c r="I52" s="3">
-        <v>6840000</v>
-      </c>
-      <c r="J52" s="3">
-        <v>4093000</v>
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K52" s="3">
         <v>2998000</v>
@@ -2141,25 +2141,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>50011000</v>
+        <v>13470000</v>
       </c>
       <c r="E57" s="3">
-        <v>48559000</v>
+        <v>12743000</v>
       </c>
       <c r="F57" s="3">
-        <v>43505000</v>
+        <v>11258000</v>
       </c>
       <c r="G57" s="3">
-        <v>42459000</v>
+        <v>9543000</v>
       </c>
       <c r="H57" s="3">
-        <v>29084000</v>
+        <v>9583000</v>
       </c>
       <c r="I57" s="3">
-        <v>23740000</v>
+        <v>6873000</v>
       </c>
       <c r="J57" s="3">
-        <v>17821000</v>
+        <v>5158000</v>
       </c>
       <c r="K57" s="3">
         <v>11879000</v>
@@ -2174,25 +2174,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>58175000</v>
+        <v>59310000</v>
       </c>
       <c r="E58" s="3">
-        <v>43297000</v>
+        <v>44483000</v>
       </c>
       <c r="F58" s="3">
-        <v>31879000</v>
+        <v>33947000</v>
       </c>
       <c r="G58" s="3">
-        <v>21287000</v>
+        <v>22102000</v>
       </c>
       <c r="H58" s="3">
-        <v>16329000</v>
+        <v>16479000</v>
       </c>
       <c r="I58" s="3">
-        <v>11624000</v>
+        <v>11599000</v>
       </c>
       <c r="J58" s="3">
-        <v>10778000</v>
+        <v>10756000</v>
       </c>
       <c r="K58" s="3">
         <v>8973000</v>
@@ -2207,25 +2207,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>0</v>
+        <v>118000</v>
       </c>
       <c r="E59" s="3">
-        <v>0</v>
+        <v>876000</v>
       </c>
       <c r="F59" s="3">
-        <v>0</v>
+        <v>3148000</v>
       </c>
       <c r="G59" s="3">
-        <v>0</v>
+        <v>2359000</v>
       </c>
       <c r="H59" s="3">
-        <v>0</v>
+        <v>1690000</v>
       </c>
       <c r="I59" s="3">
-        <v>0</v>
+        <v>812000</v>
       </c>
       <c r="J59" s="3">
-        <v>0</v>
+        <v>1424000</v>
       </c>
       <c r="K59" s="3">
         <v>0</v>
@@ -2240,25 +2240,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>72898000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>58102000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>48353000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>34004000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>27752000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>19284000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>17338000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2273,25 +2273,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>188299000</v>
+        <v>187164000</v>
       </c>
       <c r="E61" s="3">
-        <v>182357000</v>
+        <v>181171000</v>
       </c>
       <c r="F61" s="3">
-        <v>155864000</v>
+        <v>153796000</v>
       </c>
       <c r="G61" s="3">
-        <v>137580000</v>
+        <v>136765000</v>
       </c>
       <c r="H61" s="3">
-        <v>143275000</v>
+        <v>134626000</v>
       </c>
       <c r="I61" s="3">
-        <v>108995000</v>
+        <v>108771000</v>
       </c>
       <c r="J61" s="3">
-        <v>69857000</v>
+        <v>69735000</v>
       </c>
       <c r="K61" s="3">
         <v>58080000</v>
@@ -2306,25 +2306,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>24987000</v>
+        <v>36804000</v>
       </c>
       <c r="E62" s="3">
-        <v>23190000</v>
+        <v>36930000</v>
       </c>
       <c r="F62" s="3">
-        <v>20328000</v>
+        <v>32744000</v>
       </c>
       <c r="G62" s="3">
-        <v>15913000</v>
+        <v>32920000</v>
       </c>
       <c r="H62" s="3">
-        <v>14849000</v>
+        <v>28770000</v>
       </c>
       <c r="I62" s="3">
-        <v>12236000</v>
+        <v>18115000</v>
       </c>
       <c r="J62" s="3">
-        <v>11409000</v>
+        <v>14105000</v>
       </c>
       <c r="K62" s="3">
         <v>9640000</v>
@@ -2438,25 +2438,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>444318000</v>
+        <v>321853000</v>
       </c>
       <c r="E66" s="3">
-        <v>397531000</v>
+        <v>299393000</v>
       </c>
       <c r="F66" s="3">
-        <v>344648000</v>
+        <v>256262000</v>
       </c>
       <c r="G66" s="3">
-        <v>307858000</v>
+        <v>221054000</v>
       </c>
       <c r="H66" s="3">
-        <v>288956000</v>
+        <v>207123000</v>
       </c>
       <c r="I66" s="3">
-        <v>226466000</v>
+        <v>159131000</v>
       </c>
       <c r="J66" s="3">
-        <v>164476000</v>
+        <v>112848000</v>
       </c>
       <c r="K66" s="3">
         <v>133373000</v>
@@ -2618,25 +2618,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>19692000</v>
+        <v>18006000</v>
       </c>
       <c r="E72" s="3">
-        <v>18904000</v>
+        <v>18006000</v>
       </c>
       <c r="F72" s="3">
-        <v>19115000</v>
+        <v>17705000</v>
       </c>
       <c r="G72" s="3">
-        <v>15952000</v>
+        <v>15178000</v>
       </c>
       <c r="H72" s="3">
-        <v>16408000</v>
+        <v>16026000</v>
       </c>
       <c r="I72" s="3">
-        <v>14551000</v>
+        <v>14244000</v>
       </c>
       <c r="J72" s="3">
-        <v>11899000</v>
+        <v>11864000</v>
       </c>
       <c r="K72" s="3">
         <v>11182000</v>
@@ -2854,25 +2854,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>964000</v>
+        <v>1130000</v>
       </c>
       <c r="E81" s="3">
-        <v>1906000</v>
+        <v>2056000</v>
       </c>
       <c r="F81" s="3">
-        <v>3818000</v>
+        <v>3966000</v>
       </c>
       <c r="G81" s="3">
-        <v>-275000</v>
+        <v>-134000</v>
       </c>
       <c r="H81" s="3">
-        <v>2655000</v>
+        <v>2807000</v>
       </c>
       <c r="I81" s="3">
-        <v>3433000</v>
+        <v>3584000</v>
       </c>
       <c r="J81" s="3">
-        <v>1317000</v>
+        <v>1462000</v>
       </c>
       <c r="K81" s="3">
         <v>1518000</v>
@@ -2902,25 +2902,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>9075000</v>
+        <v>6422000</v>
       </c>
       <c r="E83" s="3">
-        <v>7683000</v>
+        <v>5545000</v>
       </c>
       <c r="F83" s="3">
-        <v>6437000</v>
+        <v>4960000</v>
       </c>
       <c r="G83" s="3">
-        <v>5791000</v>
+        <v>4481000</v>
       </c>
       <c r="H83" s="3">
-        <v>4876000</v>
+        <v>3735000</v>
       </c>
       <c r="I83" s="3">
-        <v>3102000</v>
+        <v>2443000</v>
       </c>
       <c r="J83" s="3">
-        <v>2345000</v>
+        <v>1903000</v>
       </c>
       <c r="K83" s="3">
         <v>2020000</v>
@@ -3100,25 +3100,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>6456000</v>
+        <v>6467000</v>
       </c>
       <c r="E89" s="3">
-        <v>8909000</v>
+        <v>8751000</v>
       </c>
       <c r="F89" s="3">
-        <v>7667000</v>
+        <v>7874000</v>
       </c>
       <c r="G89" s="3">
-        <v>8364000</v>
+        <v>8341000</v>
       </c>
       <c r="H89" s="3">
-        <v>6321000</v>
+        <v>6328000</v>
       </c>
       <c r="I89" s="3">
-        <v>5158000</v>
+        <v>5159000</v>
       </c>
       <c r="J89" s="3">
-        <v>3985000</v>
+        <v>4005000</v>
       </c>
       <c r="K89" s="3">
         <v>3083000</v>
@@ -3148,25 +3148,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-16282000</v>
+        <v>-8069000</v>
       </c>
       <c r="E91" s="3">
-        <v>-16900000</v>
+        <v>-7236000</v>
       </c>
       <c r="F91" s="3">
-        <v>-18167000</v>
+        <v>-6881000</v>
       </c>
       <c r="G91" s="3">
-        <v>-9123000</v>
+        <v>-4012000</v>
       </c>
       <c r="H91" s="3">
-        <v>-9974000</v>
+        <v>-3053000</v>
       </c>
       <c r="I91" s="3">
-        <v>-4841000</v>
+        <v>-1962000</v>
       </c>
       <c r="J91" s="3">
-        <v>-3804000</v>
+        <v>-1690000</v>
       </c>
       <c r="K91" s="3">
         <v>-3441000</v>
@@ -3295,25 +3295,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-602000</v>
+        <v>436000</v>
       </c>
       <c r="E96" s="3">
-        <v>-1029000</v>
+        <v>879000</v>
       </c>
       <c r="F96" s="3">
-        <v>-1486000</v>
+        <v>800000</v>
       </c>
       <c r="G96" s="3">
-        <v>-867000</v>
+        <v>726000</v>
       </c>
       <c r="H96" s="3">
-        <v>-772000</v>
+        <v>620000</v>
       </c>
       <c r="I96" s="3">
-        <v>-726000</v>
+        <v>575000</v>
       </c>
       <c r="J96" s="3">
-        <v>-685000</v>
+        <v>540000</v>
       </c>
       <c r="K96" s="3">
         <v>-633000</v>
@@ -3493,25 +3493,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-3174000</v>
+        <v>-3163000</v>
       </c>
       <c r="E102" s="3">
-        <v>1702000</v>
+        <v>1544000</v>
       </c>
       <c r="F102" s="3">
-        <v>2761000</v>
+        <v>2968000</v>
       </c>
       <c r="G102" s="3">
-        <v>3155000</v>
+        <v>3132000</v>
       </c>
       <c r="H102" s="3">
-        <v>-1612000</v>
+        <v>-1605000</v>
       </c>
       <c r="I102" s="3">
-        <v>3251000</v>
+        <v>3252000</v>
       </c>
       <c r="J102" s="3">
-        <v>840000</v>
+        <v>860000</v>
       </c>
       <c r="K102" s="3">
         <v>1525000</v>

--- a/AAII_Financials/Yearly/BN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
   <si>
     <t>BN</t>
   </si>
@@ -656,159 +656,171 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>88735000</v>
+      </c>
+      <c r="E8" s="3">
         <v>97992000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>95382000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>78182000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>62673000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>71609000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>58489000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>41999000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>24411000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19913000</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>58199000</v>
+      </c>
+      <c r="E9" s="3">
         <v>77808000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>75507000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>64000000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>53177000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>52728000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>45519000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>32388000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12487000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>9988000</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>30536000</v>
+      </c>
+      <c r="E10" s="3">
         <v>20184000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>19875000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>14182000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>9496000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>18881000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>12970000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9611000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>11924000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9925000</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -822,8 +834,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -854,9 +867,12 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -887,75 +903,84 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>319000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-4512000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-1397000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-8232000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>272000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>10000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1837000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-784000</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>9737000</v>
+      </c>
+      <c r="E15" s="3">
         <v>9075000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7683000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6437000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5791000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4876000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3102000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2345000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2020000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>1695000</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -966,74 +991,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>68012000</v>
+      </c>
+      <c r="E17" s="3">
         <v>81478000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>78633000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>64116000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>53278000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>57702000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>48725000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>34828000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>21418000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>15048000</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>20723000</v>
+      </c>
+      <c r="E18" s="3">
         <v>16514000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>16749000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>14066000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>9395000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>13907000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>9764000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>7171000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2993000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4865000</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1047,173 +1079,189 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1273000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-593000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>780000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-18000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>366000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>821000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-493000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-817000</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>29187000</v>
+      </c>
+      <c r="E21" s="3">
         <v>26182000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>23652000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>20521000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>14820000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>17962000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>13359000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>10333000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5013000</v>
       </c>
-      <c r="L21" s="3" t="s">
+      <c r="M21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>16296000</v>
+      </c>
+      <c r="E22" s="3">
         <v>15503000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>10702000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>7604000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7213000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7227000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>4854000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3608000</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2835000</v>
+      </c>
+      <c r="E23" s="3">
         <v>6116000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6664000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>14712000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1544000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5849000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7240000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>5164000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2993000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4865000</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>982000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1011000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1469000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2324000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>837000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>495000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-248000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>613000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-345000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>196000</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1244,75 +1292,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1853000</v>
+      </c>
+      <c r="E26" s="3">
         <v>5105000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5195000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>12388000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>707000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5354000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>7488000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>4551000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3338000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>4669000</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>473000</v>
+      </c>
+      <c r="E27" s="3">
         <v>964000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1906000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>3792000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-182000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2581000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3328000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1317000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1518000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2207000</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1343,9 +1400,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1376,9 +1436,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1409,9 +1472,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1442,75 +1508,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1273000</v>
+      </c>
+      <c r="E32" s="3">
         <v>593000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-780000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>18000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-366000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-821000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>493000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>817000</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>641000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1130000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2056000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3966000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-134000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2807000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3584000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1462000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1518000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2207000</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1541,80 +1616,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>641000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1130000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2056000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3966000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-134000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2807000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3584000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1462000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1518000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2207000</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1628,8 +1712,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1643,41 +1728,45 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>15051000</v>
+      </c>
+      <c r="E41" s="3">
         <v>11222000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14396000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12694000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>9933000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6778000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8390000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5139000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>4299000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2774000</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1708,240 +1797,264 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>40509000</v>
+      </c>
+      <c r="E43" s="3">
         <v>24783000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>22107000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>14169000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12809000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12988000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>10985000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8823000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4294000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7044000</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>8458000</v>
+      </c>
+      <c r="E44" s="3">
         <v>11412000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>12843000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>11415000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>10360000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>10272000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6989000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6311000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5349000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5281000</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>2489000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2830000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>11958000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5917000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3502000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2185000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1605000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3448000</v>
       </c>
-      <c r="L45" s="3" t="s">
+      <c r="M45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>64018000</v>
+      </c>
+      <c r="E46" s="3">
         <v>63539000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>65399000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>60664000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>47749000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>40771000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>35980000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>26252000</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3">
+        <v>0</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>68310000</v>
+      </c>
+      <c r="E47" s="3">
         <v>77544000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>66041000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>59809000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>56361000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>51307000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>38056000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>35180000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>29677000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>29372000</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>256684000</v>
+      </c>
+      <c r="E48" s="3">
         <v>271769000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>239368000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>216354000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>196876000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>186059000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>151936000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>110265000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>99518000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>84437000</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>71802000</v>
+      </c>
+      <c r="E49" s="3">
         <v>73905000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>67073000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>50836000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>39372000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>42260000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>27577000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>19559000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>9856000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>7713000</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1972,9 +2085,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2005,14 +2121,17 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
+      <c r="D52" s="3">
+        <v>25887000</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>8</v>
@@ -2032,15 +2151,18 @@
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3">
         <v>2998000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2893000</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2071,42 +2193,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>490424000</v>
+      </c>
+      <c r="E54" s="3">
         <v>490095000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>441284000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>391003000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>343696000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>323969000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>256281000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>192720000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>159826000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>139514000</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2120,8 +2248,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2135,206 +2264,225 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>60223000</v>
+      </c>
+      <c r="E57" s="3">
         <v>13470000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>12743000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>11258000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>9543000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9583000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6873000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5158000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11879000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11276000</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
         <v>59310000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>44483000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>33947000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>22102000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>16479000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>11599000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10756000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8973000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>11484000</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
         <v>118000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>876000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3148000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2359000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1690000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>812000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1424000</v>
       </c>
-      <c r="K59" s="3">
-        <v>0</v>
-      </c>
       <c r="L59" s="3">
         <v>0</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>60223000</v>
+      </c>
+      <c r="E60" s="3">
         <v>72898000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>58102000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>48353000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>34004000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>27752000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>19284000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17338000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3">
+        <v>0</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>239551000</v>
+      </c>
+      <c r="E61" s="3">
         <v>187164000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>181171000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>153796000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>136765000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>134626000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>108771000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>69735000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>58080000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>48946000</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3">
         <v>36804000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>36930000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>32744000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>32920000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>28770000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>18115000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>14105000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>9640000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8785000</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2365,9 +2513,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2398,9 +2549,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2431,42 +2585,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>325041000</v>
+      </c>
+      <c r="E66" s="3">
         <v>321853000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>299393000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>256262000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>221054000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>207123000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>159131000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>112848000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>133373000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>114207000</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2480,8 +2640,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2512,9 +2673,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2545,9 +2709,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2555,7 +2722,7 @@
         <v>4103000</v>
       </c>
       <c r="E70" s="3">
-        <v>4145000</v>
+        <v>4103000</v>
       </c>
       <c r="F70" s="3">
         <v>4145000</v>
@@ -2567,20 +2734,23 @@
         <v>4145000</v>
       </c>
       <c r="I70" s="3">
+        <v>4145000</v>
+      </c>
+      <c r="J70" s="3">
         <v>4168000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>4192000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>3954000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>3739000</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2611,42 +2781,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>18006000</v>
+      <c r="D72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E72" s="3">
         <v>18006000</v>
       </c>
       <c r="F72" s="3">
+        <v>18006000</v>
+      </c>
+      <c r="G72" s="3">
         <v>17705000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>15178000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>16026000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>14244000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>11864000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>11182000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>10507000</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2677,9 +2853,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2710,9 +2889,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2743,42 +2925,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>41874000</v>
+      </c>
+      <c r="E76" s="3">
         <v>41674000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>39608000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>42210000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>31693000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>30868000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>25647000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>24052000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>22499000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>21568000</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2809,80 +2997,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>641000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1130000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2056000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3966000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-134000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2807000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3584000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1462000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1518000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2207000</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2896,41 +3093,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3">
         <v>6422000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5545000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>4960000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4481000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3735000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2443000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1903000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2020000</v>
       </c>
-      <c r="L83" s="3" t="s">
+      <c r="M83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2961,9 +3162,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2994,9 +3198,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3027,9 +3234,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3060,9 +3270,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3093,42 +3306,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
         <v>6467000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8751000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>7874000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8341000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6328000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5159000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4005000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3083000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2574000</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3142,41 +3361,45 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8069000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7236000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6881000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4012000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3053000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1962000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1690000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3441000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3095000</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3207,9 +3430,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3240,42 +3466,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3">
         <v>-29762000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-39650000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-21045000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13873000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-36674000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-19833000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11394000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8557000</v>
       </c>
-      <c r="L94" s="3" t="s">
+      <c r="M94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3289,41 +3521,45 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>436000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>879000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>800000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>726000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>620000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>575000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>540000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-633000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-542000</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3354,9 +3590,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3387,9 +3626,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3420,106 +3662,118 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
         <v>19927000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>32460000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>16261000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>8698000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>28746000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>18136000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>8185000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6993000</v>
       </c>
-      <c r="L100" s="3" t="s">
+      <c r="M100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3">
         <v>205000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-17000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-122000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-34000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-210000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>64000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>6000</v>
       </c>
-      <c r="L101" s="3" t="s">
+      <c r="M101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3163000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1544000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2968000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3132000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1605000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3252000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>860000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1525000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-503000</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/BN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>BN</t>
   </si>
@@ -753,7 +753,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>58199000</v>
+        <v>64203000</v>
       </c>
       <c r="E9" s="3">
         <v>77808000</v>
@@ -789,7 +789,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>30536000</v>
+        <v>24532000</v>
       </c>
       <c r="E10" s="3">
         <v>20184000</v>
@@ -913,7 +913,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>319000</v>
+        <v>458000</v>
       </c>
       <c r="E14" s="3">
         <v>-4512000</v>
@@ -1086,7 +1086,7 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1273000</v>
+        <v>815000</v>
       </c>
       <c r="E20" s="3">
         <v>-593000</v>
@@ -1122,7 +1122,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>29187000</v>
+        <v>29645000</v>
       </c>
       <c r="E21" s="3">
         <v>26182000</v>
@@ -1158,7 +1158,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>16296000</v>
+        <v>16615000</v>
       </c>
       <c r="E22" s="3">
         <v>15503000</v>
@@ -1518,7 +1518,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1273000</v>
+        <v>-815000</v>
       </c>
       <c r="E32" s="3">
         <v>593000</v>
@@ -1807,7 +1807,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>40509000</v>
+        <v>22635000</v>
       </c>
       <c r="E43" s="3">
         <v>24783000</v>
@@ -1878,8 +1878,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>8</v>
+      <c r="D45" s="3">
+        <v>10291000</v>
       </c>
       <c r="E45" s="3">
         <v>2489000</v>
@@ -1915,7 +1915,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>64018000</v>
+        <v>72160000</v>
       </c>
       <c r="E46" s="3">
         <v>63539000</v>
@@ -1951,7 +1951,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>68310000</v>
+        <v>86055000</v>
       </c>
       <c r="E47" s="3">
         <v>77544000</v>
@@ -2130,8 +2130,8 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>25887000</v>
+      <c r="D52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>8</v>
@@ -2271,7 +2271,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>60223000</v>
+        <v>13202000</v>
       </c>
       <c r="E57" s="3">
         <v>13470000</v>
@@ -2307,10 +2307,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>52973000</v>
       </c>
       <c r="E58" s="3">
-        <v>59310000</v>
+        <v>59306000</v>
       </c>
       <c r="F58" s="3">
         <v>44483000</v>
@@ -2342,8 +2342,8 @@
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>8</v>
+      <c r="D59" s="3">
+        <v>4721000</v>
       </c>
       <c r="E59" s="3">
         <v>118000</v>
@@ -2379,10 +2379,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>60223000</v>
+        <v>70896000</v>
       </c>
       <c r="E60" s="3">
-        <v>72898000</v>
+        <v>72894000</v>
       </c>
       <c r="F60" s="3">
         <v>58102000</v>
@@ -2415,10 +2415,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>239551000</v>
+        <v>196240000</v>
       </c>
       <c r="E61" s="3">
-        <v>187164000</v>
+        <v>187168000</v>
       </c>
       <c r="F61" s="3">
         <v>181171000</v>
@@ -2450,8 +2450,8 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>8</v>
+      <c r="D62" s="3">
+        <v>32638000</v>
       </c>
       <c r="E62" s="3">
         <v>36804000</v>
@@ -2790,8 +2790,8 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>8</v>
+      <c r="D72" s="3">
+        <v>17066000</v>
       </c>
       <c r="E72" s="3">
         <v>18006000</v>
@@ -3099,8 +3099,8 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
+      <c r="D83" s="3">
+        <v>7217000</v>
       </c>
       <c r="E83" s="3">
         <v>6422000</v>
@@ -3315,8 +3315,8 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>8</v>
+      <c r="D89" s="3">
+        <v>7569000</v>
       </c>
       <c r="E89" s="3">
         <v>6467000</v>
@@ -3367,8 +3367,8 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>8</v>
+      <c r="D91" s="3">
+        <v>-11172000</v>
       </c>
       <c r="E91" s="3">
         <v>-8069000</v>
@@ -3475,8 +3475,8 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
+      <c r="D94" s="3">
+        <v>-29964000</v>
       </c>
       <c r="E94" s="3">
         <v>-29762000</v>
@@ -3528,7 +3528,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>495000</v>
       </c>
       <c r="E96" s="3">
         <v>436000</v>
@@ -3671,8 +3671,8 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
+      <c r="D100" s="3">
+        <v>26900000</v>
       </c>
       <c r="E100" s="3">
         <v>19927000</v>
@@ -3707,8 +3707,8 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>8</v>
+      <c r="D101" s="3">
+        <v>-461000</v>
       </c>
       <c r="E101" s="3">
         <v>205000</v>
@@ -3744,7 +3744,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>4044000</v>
       </c>
       <c r="E102" s="3">
         <v>-3163000</v>

--- a/AAII_Financials/Yearly/BN_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BN_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
   <si>
     <t>BN</t>
   </si>
@@ -656,171 +656,183 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>77657000</v>
+      </c>
+      <c r="E8" s="3">
         <v>88735000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>97992000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>95382000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>78182000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>62673000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>71609000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>58489000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>41999000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>24411000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19913000</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>52893000</v>
+      </c>
+      <c r="E9" s="3">
         <v>64203000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>77808000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>75507000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>64000000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>53177000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>52728000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>45519000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>32388000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12487000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>9988000</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>24764000</v>
+      </c>
+      <c r="E10" s="3">
         <v>24532000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>20184000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>19875000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>14182000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>9496000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>18881000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>12970000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9611000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>11924000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9925000</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -835,8 +847,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -870,9 +883,12 @@
       <c r="M12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -906,81 +922,90 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E14" s="3">
         <v>458000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-4512000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1397000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-8232000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>272000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>10000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1837000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-784000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>10379000</v>
+      </c>
+      <c r="E15" s="3">
         <v>9737000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>9075000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7683000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6437000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5791000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4876000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3102000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2345000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2020000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1695000</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -992,80 +1017,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>57051000</v>
+      </c>
+      <c r="E17" s="3">
         <v>68012000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>81478000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>78633000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>64116000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>53278000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>57702000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>48725000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>34828000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>21418000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>15048000</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>20606000</v>
+      </c>
+      <c r="E18" s="3">
         <v>20723000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>16514000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>16749000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>14066000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>9395000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>13907000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>9764000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>7171000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2993000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4865000</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1080,188 +1112,204 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-867000</v>
+      </c>
+      <c r="E20" s="3">
         <v>815000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-593000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>780000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-18000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>366000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>821000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-493000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-817000</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>31852000</v>
+      </c>
+      <c r="E21" s="3">
         <v>29645000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>26182000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>23652000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>20521000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>14820000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>17962000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>13359000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10333000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5013000</v>
       </c>
-      <c r="M21" s="3" t="s">
+      <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>17100000</v>
+      </c>
+      <c r="E22" s="3">
         <v>16615000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>15503000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>10702000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7604000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7213000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7227000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4854000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3608000</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4370000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2835000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>6116000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6664000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>14712000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1544000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5849000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7240000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5164000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2993000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>4865000</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1135000</v>
+      </c>
+      <c r="E24" s="3">
         <v>982000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1011000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1469000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2324000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>837000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>495000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-248000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>613000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-345000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>196000</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1295,81 +1343,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3235000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1853000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5105000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5195000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>12388000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>707000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5354000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>7488000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>4551000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3338000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>4669000</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1140000</v>
+      </c>
+      <c r="E27" s="3">
         <v>473000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>964000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1906000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3792000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-182000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2581000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3328000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1317000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1518000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2207000</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1403,9 +1460,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1439,9 +1499,12 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1475,9 +1538,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1511,81 +1577,90 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>867000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-815000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>593000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-780000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>18000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-366000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-821000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>493000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>817000</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1307000</v>
+      </c>
+      <c r="E33" s="3">
         <v>641000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1130000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2056000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3966000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-134000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2807000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3584000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1462000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1518000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2207000</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1619,86 +1694,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1307000</v>
+      </c>
+      <c r="E35" s="3">
         <v>641000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1130000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2056000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3966000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-134000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2807000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3584000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1462000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1518000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2207000</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1713,8 +1797,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1729,44 +1814,48 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16242000</v>
+      </c>
+      <c r="E41" s="3">
         <v>15051000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11222000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>14396000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12694000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>9933000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6778000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8390000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5139000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4299000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2774000</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1800,261 +1889,285 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>25727000</v>
+      </c>
+      <c r="E43" s="3">
         <v>22635000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24783000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>22107000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>14169000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12809000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12988000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>10985000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8823000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4294000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7044000</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>8849000</v>
+      </c>
+      <c r="E44" s="3">
         <v>8458000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>11412000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>12843000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>11415000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>10360000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>10272000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6989000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6311000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5349000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5281000</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12780000</v>
+      </c>
+      <c r="E45" s="3">
         <v>10291000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2489000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2830000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11958000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5917000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3502000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2185000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1605000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3448000</v>
       </c>
-      <c r="M45" s="3" t="s">
+      <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>80331000</v>
+      </c>
+      <c r="E46" s="3">
         <v>72160000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>63539000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>65399000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>60664000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>47749000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>40771000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>35980000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>26252000</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3">
+        <v>0</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>100963000</v>
+      </c>
+      <c r="E47" s="3">
         <v>86055000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>77544000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>66041000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>59809000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>56361000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>51307000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>38056000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>35180000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>29677000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>29372000</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>251605000</v>
+      </c>
+      <c r="E48" s="3">
         <v>256684000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>271769000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>239368000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>216354000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>196876000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>186059000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>151936000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>110265000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>99518000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>84437000</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>81851000</v>
+      </c>
+      <c r="E49" s="3">
         <v>71802000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>73905000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>67073000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>50836000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>39372000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>42260000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>27577000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>19559000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>9856000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7713000</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2088,9 +2201,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2124,9 +2240,12 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2154,15 +2273,18 @@
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="3">
         <v>2998000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2893000</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2196,45 +2318,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>518971000</v>
+      </c>
+      <c r="E54" s="3">
         <v>490424000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>490095000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>441284000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>391003000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>343696000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>323969000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>256281000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>192720000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>159826000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>139514000</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2249,8 +2377,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2265,224 +2394,243 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16252000</v>
+      </c>
+      <c r="E57" s="3">
         <v>13202000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13470000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>12743000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11258000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>9543000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>9583000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6873000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>5158000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11879000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11276000</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>52973000</v>
+        <v>41353000</v>
       </c>
       <c r="E58" s="3">
+        <v>39165000</v>
+      </c>
+      <c r="F58" s="3">
         <v>59306000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>44483000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>33947000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>22102000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>16479000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>11599000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10756000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8973000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>11484000</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5891000</v>
+      </c>
+      <c r="E59" s="3">
         <v>4721000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>118000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>876000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3148000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2359000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1690000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>812000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1424000</v>
       </c>
-      <c r="L59" s="3">
-        <v>0</v>
-      </c>
       <c r="M59" s="3">
         <v>0</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3">
+        <v>0</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>70896000</v>
+        <v>63496000</v>
       </c>
       <c r="E60" s="3">
+        <v>57088000</v>
+      </c>
+      <c r="F60" s="3">
         <v>72894000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>58102000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>48353000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>34004000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>27752000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>19284000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>17338000</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3">
+        <v>0</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>196240000</v>
+        <v>231268000</v>
       </c>
       <c r="E61" s="3">
+        <v>210048000</v>
+      </c>
+      <c r="F61" s="3">
         <v>187168000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>181171000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>153796000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>136765000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>134626000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>108771000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>69735000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>58080000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>48946000</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>31004000</v>
+      </c>
+      <c r="E62" s="3">
         <v>32638000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>36804000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>36930000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>32744000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>32920000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>28770000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>18115000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>14105000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>9640000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8785000</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2516,9 +2664,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2552,9 +2703,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2588,45 +2742,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>352777000</v>
+      </c>
+      <c r="E66" s="3">
         <v>325041000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>321853000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>299393000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>256262000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>221054000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>207123000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>159131000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>112848000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>133373000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>114207000</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2641,8 +2801,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2676,9 +2837,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2712,20 +2876,23 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>4103000</v>
+        <v>4090000</v>
       </c>
       <c r="E70" s="3">
         <v>4103000</v>
       </c>
       <c r="F70" s="3">
-        <v>4145000</v>
+        <v>4103000</v>
       </c>
       <c r="G70" s="3">
         <v>4145000</v>
@@ -2737,20 +2904,23 @@
         <v>4145000</v>
       </c>
       <c r="J70" s="3">
+        <v>4145000</v>
+      </c>
+      <c r="K70" s="3">
         <v>4168000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>4192000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>3954000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>3739000</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2784,45 +2954,51 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>16665000</v>
+      </c>
+      <c r="E72" s="3">
         <v>17066000</v>
-      </c>
-      <c r="E72" s="3">
-        <v>18006000</v>
       </c>
       <c r="F72" s="3">
         <v>18006000</v>
       </c>
       <c r="G72" s="3">
+        <v>18006000</v>
+      </c>
+      <c r="H72" s="3">
         <v>17705000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15178000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>16026000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>14244000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>11864000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>11182000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>10507000</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2856,9 +3032,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2892,9 +3071,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2928,45 +3110,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>43796000</v>
+      </c>
+      <c r="E76" s="3">
         <v>41874000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>41674000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>39608000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>42210000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>31693000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>30868000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>25647000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>24052000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>22499000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21568000</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3000,86 +3188,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1307000</v>
+      </c>
+      <c r="E81" s="3">
         <v>641000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1130000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2056000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3966000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-134000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2807000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3584000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1462000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1518000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2207000</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3094,44 +3291,48 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7643000</v>
+      </c>
+      <c r="E83" s="3">
         <v>7217000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6422000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5545000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>4960000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4481000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3735000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2443000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1903000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2020000</v>
       </c>
-      <c r="M83" s="3" t="s">
+      <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3165,9 +3366,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3201,9 +3405,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3237,9 +3444,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3273,9 +3483,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3309,45 +3522,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10958000</v>
+      </c>
+      <c r="E89" s="3">
         <v>7569000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>6467000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8751000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7874000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8341000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6328000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5159000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4005000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3083000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2574000</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3362,44 +3581,48 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14752000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11172000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8069000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7236000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6881000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4012000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3053000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1962000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1690000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3441000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3095000</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3433,9 +3656,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3469,45 +3695,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-31777000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-29964000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-29762000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-39650000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-21045000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13873000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-36674000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-19833000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11394000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8557000</v>
       </c>
-      <c r="M94" s="3" t="s">
+      <c r="N94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3522,44 +3754,48 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>552000</v>
+      </c>
+      <c r="E96" s="3">
         <v>495000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>436000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>879000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>800000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>726000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>620000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>575000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>540000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-633000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-542000</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3593,9 +3829,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3629,9 +3868,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3665,115 +3907,127 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>21687000</v>
+      </c>
+      <c r="E100" s="3">
         <v>26900000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>19927000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>32460000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>16261000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>8698000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>28746000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>18136000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>8185000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>6993000</v>
       </c>
-      <c r="M100" s="3" t="s">
+      <c r="N100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>252000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-461000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>205000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-17000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-122000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-34000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-210000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>64000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>6000</v>
       </c>
-      <c r="M101" s="3" t="s">
+      <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1120000</v>
+      </c>
+      <c r="E102" s="3">
         <v>4044000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-3163000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1544000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2968000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3132000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1605000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3252000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>860000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1525000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-503000</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
